--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.5</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.61</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.61</t>
+    <t>0.9.71</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.71</t>
+    <t>0.9.72</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.72</t>
+    <t>0.9.73</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.73</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-NoDomainVitalSignsBloodpressureDiastolicFormulaExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
